--- a/JLPT-N2-Output.xlsx
+++ b/JLPT-N2-Output.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D158"/>
+  <dimension ref="A1:D116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,17 +445,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>見誤る</t>
+          <t>副作用</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>みあやまる</t>
+          <t>ふくさよう</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>to misjudge</t>
+          <t>side effect</t>
         </is>
       </c>
     </row>
@@ -465,17 +465,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>近々</t>
+          <t>真向い</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ちかぢか</t>
+          <t>まむかい</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>shortly</t>
+          <t>right opposite</t>
         </is>
       </c>
     </row>
@@ -485,17 +485,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>定める</t>
+          <t>手につかない</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>さだめる</t>
+          <t>てにつかない</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>to enact</t>
+          <t>can't focus [concentrate] on</t>
         </is>
       </c>
     </row>
@@ -505,17 +505,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>退化</t>
+          <t>内科</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>たいか</t>
+          <t>ないか</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>degeneration</t>
+          <t>internal medicine</t>
         </is>
       </c>
     </row>
@@ -525,17 +525,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>法事</t>
+          <t>出荷</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ほうじ</t>
+          <t>しゅっか</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>memorial service</t>
+          <t>shipment</t>
         </is>
       </c>
     </row>
@@ -545,17 +545,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>粗筋</t>
+          <t>案の定</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>あらすじ</t>
+          <t>あんのじょう</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>outline</t>
+          <t>as expected</t>
         </is>
       </c>
     </row>
@@ -565,17 +565,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>言い張る</t>
+          <t>惜しむ</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>いいはる</t>
+          <t>おしむ</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>to insist on, to stick to one's point</t>
+          <t>to regret, to begrudge</t>
         </is>
       </c>
     </row>
@@ -585,17 +585,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>見かける</t>
+          <t>貯蓄</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>みかける</t>
+          <t>ちょちく</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>to happen to see</t>
+          <t>savings</t>
         </is>
       </c>
     </row>
@@ -605,17 +605,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>顔つき</t>
+          <t>訴えかける</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>かおつき</t>
+          <t>うったえかける</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>looks, facial expression</t>
+          <t>to appeal</t>
         </is>
       </c>
     </row>
@@ -625,17 +625,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>活発</t>
+          <t>通りかかる</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>かっぱつ</t>
+          <t>とおりかかる</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>lively</t>
+          <t>to happen to pass by</t>
         </is>
       </c>
     </row>
@@ -645,17 +645,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>訂正</t>
+          <t>及ぶ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ていせい</t>
+          <t>およぶ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>correction</t>
+          <t>to reach, to extend</t>
         </is>
       </c>
     </row>
@@ -665,17 +665,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>非公式</t>
+          <t>診断</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ひこうしき</t>
+          <t>しんだん</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>informal</t>
+          <t>diagnosis</t>
         </is>
       </c>
     </row>
@@ -685,17 +685,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>身が入る</t>
+          <t>攻める</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>みがはいる</t>
+          <t>せめる</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>to concentrate on</t>
+          <t>to attack</t>
         </is>
       </c>
     </row>
@@ -705,17 +705,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>品種改良</t>
+          <t>託児所</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ひんしゅかいりょう</t>
+          <t>たくじしょ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>selective breeding</t>
+          <t>nursery</t>
         </is>
       </c>
     </row>
@@ -725,17 +725,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>法廷</t>
+          <t>身につける</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ほうてい</t>
+          <t>みにつける</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>court</t>
+          <t>to learn, to cultivate</t>
         </is>
       </c>
     </row>
@@ -745,17 +745,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>盛大</t>
+          <t>見かける</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>せいだい</t>
+          <t>みかける</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>magnificent</t>
+          <t>to happen to see</t>
         </is>
       </c>
     </row>
@@ -765,17 +765,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>～代</t>
+          <t>築く</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>だい</t>
+          <t>きずく</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>～ fee [bill, fare]</t>
+          <t>to build</t>
         </is>
       </c>
     </row>
@@ -783,21 +783,9 @@
       <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>傑作</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>けっさく</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>masterpiece</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -805,17 +793,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>相次いで</t>
+          <t>出場</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>あいついで</t>
+          <t>しゅつじょう</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>one after the other</t>
+          <t>participation</t>
         </is>
       </c>
     </row>
@@ -825,17 +813,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>出場</t>
+          <t>採点</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>しゅつじょう</t>
+          <t>さいてん</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>participation</t>
+          <t>scoring</t>
         </is>
       </c>
     </row>
@@ -845,17 +833,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>回数券</t>
+          <t>索引</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>かいすうけん</t>
+          <t>さくいん</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>book of tickets</t>
+          <t>index</t>
         </is>
       </c>
     </row>
@@ -865,17 +853,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>発芽</t>
+          <t>定める</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>はつが</t>
+          <t>さだめる</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>germination</t>
+          <t>to enact</t>
         </is>
       </c>
     </row>
@@ -885,17 +873,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>荒れる</t>
+          <t>思いがけない</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>あれる</t>
+          <t>おもいがけない</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>to get rough</t>
+          <t>unexpected</t>
         </is>
       </c>
     </row>
@@ -905,17 +893,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>嘆く</t>
+          <t>行方</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>なげく</t>
+          <t>ゆくえ</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>to grieve about</t>
+          <t>whereabouts</t>
         </is>
       </c>
     </row>
@@ -925,17 +913,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>普及</t>
+          <t>性能</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ふきゅう</t>
+          <t>せいのう</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>diffusion</t>
+          <t>performance</t>
         </is>
       </c>
     </row>
@@ -945,17 +933,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>惜しむ</t>
+          <t>引っかかる</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>おしむ</t>
+          <t>ひっかかる</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>to regret, to begrudge</t>
+          <t>to be stuck, to get caught</t>
         </is>
       </c>
     </row>
@@ -965,17 +953,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>面積</t>
+          <t>一段と</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>めんせき</t>
+          <t>いちだんと</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>area</t>
+          <t>even more</t>
         </is>
       </c>
     </row>
@@ -985,17 +973,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>排出量</t>
+          <t>差し押さえる</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>はいしゅつりょう</t>
+          <t>さしおさえる</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>emission amount</t>
+          <t>to seize</t>
         </is>
       </c>
     </row>
@@ -1005,17 +993,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>有害</t>
+          <t>取材</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ゆうがい</t>
+          <t>しゅざい</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>harmful</t>
+          <t>news gathering</t>
         </is>
       </c>
     </row>
@@ -1023,9 +1011,21 @@
       <c r="A31" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>担ぐ</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>かつぐ</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>to carry on one's shoulder</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -1033,17 +1033,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>出荷</t>
+          <t>嘆く</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>しゅっか</t>
+          <t>なげく</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>shipment</t>
+          <t>to grieve about</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>旧姓</t>
+          <t>有害</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>きゅうせい</t>
+          <t>ゆうがい</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>maiden name</t>
+          <t>harmful</t>
         </is>
       </c>
     </row>
@@ -1073,17 +1073,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>直ちに</t>
+          <t>補う</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ただちに</t>
+          <t>おぎなう</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>right away</t>
+          <t>to make up for</t>
         </is>
       </c>
     </row>
@@ -1093,17 +1093,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>体積</t>
+          <t>傑作</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>たいせき</t>
+          <t>けっさく</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>masterpiece</t>
         </is>
       </c>
     </row>
@@ -1113,17 +1113,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>一流～</t>
+          <t>資本金</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>いちりゅう</t>
+          <t>しほんきん</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>prestigious [leading] ～</t>
+          <t>capital</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>若干</t>
+          <t>貢献</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>じゃっかん</t>
+          <t>こうけん</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>a bit, slightly</t>
+          <t>contribution</t>
         </is>
       </c>
     </row>
@@ -1153,17 +1153,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>今にも</t>
+          <t>外科</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>いまにも</t>
+          <t>げか</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>at any moment</t>
+          <t>surgery</t>
         </is>
       </c>
     </row>
@@ -1173,17 +1173,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>承諾</t>
+          <t>引き受ける</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>しょうだく</t>
+          <t>ひきうける</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>acceptance</t>
+          <t>to undertake</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>受け継ぐ</t>
+          <t>不作法</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>うけつぐ</t>
+          <t>ぶさほう</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>to inherit</t>
+          <t>impolite, rude</t>
         </is>
       </c>
     </row>
@@ -1213,17 +1213,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>口にする</t>
+          <t>頭に来る</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>くちにする</t>
+          <t>あたまにくる</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>to talk</t>
+          <t>to get mad</t>
         </is>
       </c>
     </row>
@@ -1233,17 +1233,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>敬う</t>
+          <t>品種改良</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>うやまう</t>
+          <t>ひんしゅかいりょう</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>to respect</t>
+          <t>selective breeding</t>
         </is>
       </c>
     </row>
@@ -1253,17 +1253,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>参る</t>
+          <t>内気</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>まいる</t>
+          <t>うちき</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>to be overwhelmed by</t>
+          <t>shy</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>身につける</t>
+          <t>法事</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>みにつける</t>
+          <t>ほうじ</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>to learn, to cultivate</t>
+          <t>memorial service</t>
         </is>
       </c>
     </row>
@@ -1293,17 +1293,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>内気</t>
+          <t>前後</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>うちき</t>
+          <t>ぜんご</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>shy</t>
+          <t>around</t>
         </is>
       </c>
     </row>
@@ -1313,17 +1313,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>口が堅い</t>
+          <t>旧姓</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>くちがかたい</t>
+          <t>きゅうせい</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>tight-lipped</t>
+          <t>maiden name</t>
         </is>
       </c>
     </row>
@@ -1333,17 +1333,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>内科</t>
+          <t>敗れる</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ないか</t>
+          <t>やぶれる</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>internal medicine</t>
+          <t>to be beaten [defeated]</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>反比例</t>
+          <t>差しかかる</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>はんぴれい</t>
+          <t>さしかかる</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>inverse proportion</t>
+          <t>to approach</t>
         </is>
       </c>
     </row>
@@ -1373,17 +1373,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>危うい</t>
+          <t>果たして</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>あやうい</t>
+          <t>はたして</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>in danger, dangerous</t>
+          <t>sure enough, as expected</t>
         </is>
       </c>
     </row>
@@ -1393,17 +1393,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>深刻化</t>
+          <t>相次いで</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>しんこくか</t>
+          <t>あいついで</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>becoming more serious</t>
+          <t>one after the other</t>
         </is>
       </c>
     </row>
@@ -1413,17 +1413,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>就任</t>
+          <t>気が向く</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>しゅうにん</t>
+          <t>きがむく</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>inauguration, taking up a post</t>
+          <t>to feel like</t>
         </is>
       </c>
     </row>
@@ -1433,17 +1433,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>診断</t>
+          <t>献立</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>しんだん</t>
+          <t>こんだて</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>diagnosis</t>
+          <t>menu</t>
         </is>
       </c>
     </row>
@@ -1453,17 +1453,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>差し支えない</t>
+          <t>気に食わない</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>さしつかえない</t>
+          <t>きにくわない</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>having no objection</t>
+          <t>to dislike</t>
         </is>
       </c>
     </row>
@@ -1473,17 +1473,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>飼育</t>
+          <t>交際</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>しいく</t>
+          <t>こうさい</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>breeding</t>
+          <t>association</t>
         </is>
       </c>
     </row>
@@ -1493,17 +1493,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>児童</t>
+          <t>従来</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>じどう</t>
+          <t>じゅうらい</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>child</t>
+          <t>conventional</t>
         </is>
       </c>
     </row>
@@ -1513,17 +1513,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>宣伝</t>
+          <t>染みる</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>せんでん</t>
+          <t>しみる</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>advertisement</t>
+          <t>to soak, to pierce, to be deeply moved</t>
         </is>
       </c>
     </row>
@@ -1533,17 +1533,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>張り切る</t>
+          <t>危うい</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>はりきる</t>
+          <t>あやうい</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>to be enthusiastic</t>
+          <t>in danger, dangerous</t>
         </is>
       </c>
     </row>
@@ -1553,17 +1553,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>岬</t>
+          <t>参る</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>みさき</t>
+          <t>まいる</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>cape</t>
+          <t>to be overwhelmed by</t>
         </is>
       </c>
     </row>
@@ -1573,17 +1573,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>思いがけない</t>
+          <t>不景気</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>おもいがけない</t>
+          <t>ふけいき</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>unexpected</t>
+          <t>recession</t>
         </is>
       </c>
     </row>
@@ -1593,17 +1593,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>別荘</t>
+          <t>強気</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>べっそう</t>
+          <t>つよき</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>cottage, villa</t>
+          <t>strong, aggressive</t>
         </is>
       </c>
     </row>
@@ -1613,17 +1613,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>貢献</t>
+          <t>宣伝費</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>こうけん</t>
+          <t>せんでんひ</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>contribution</t>
+          <t>advertising cost</t>
         </is>
       </c>
     </row>
@@ -1633,17 +1633,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>犯す</t>
+          <t>顔つき</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>おかす</t>
+          <t>かおつき</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>to commit</t>
+          <t>looks, facial expression</t>
         </is>
       </c>
     </row>
@@ -1653,17 +1653,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>研修</t>
+          <t>受け継ぐ</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>けんしゅう</t>
+          <t>うけつぐ</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>training</t>
+          <t>to inherit</t>
         </is>
       </c>
     </row>
@@ -1673,17 +1673,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>強いる</t>
+          <t>盛大</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>しいる</t>
+          <t>せいだい</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>to force, to thrust</t>
+          <t>magnificent</t>
         </is>
       </c>
     </row>
@@ -1693,17 +1693,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>乏しい</t>
+          <t>若干</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>とぼしい</t>
+          <t>じゃっかん</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>scarce, poor</t>
+          <t>a bit, slightly</t>
         </is>
       </c>
     </row>
@@ -1713,17 +1713,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>取材</t>
+          <t>発芽</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>しゅざい</t>
+          <t>はつが</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>news gathering</t>
+          <t>germination</t>
         </is>
       </c>
     </row>
@@ -1733,17 +1733,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>縮小</t>
+          <t>行事</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>しゅくしょう</t>
+          <t>ぎょうじ</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>shrink</t>
+          <t>event</t>
         </is>
       </c>
     </row>
@@ -1753,17 +1753,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>外科</t>
+          <t>宣伝</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>げか</t>
+          <t>せんでん</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>surgery</t>
+          <t>advertisement</t>
         </is>
       </c>
     </row>
@@ -1773,17 +1773,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>適応</t>
+          <t>資産</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>てきおう</t>
+          <t>しさん</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>adaptation</t>
+          <t>asset</t>
         </is>
       </c>
     </row>
@@ -1791,9 +1791,21 @@
       <c r="A70" s="1" t="n">
         <v>68</v>
       </c>
-      <c r="B70" t="inlineStr"/>
-      <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>見出し</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>みだし</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>headline</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -1801,17 +1813,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>染みる</t>
+          <t>重役</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>しみる</t>
+          <t>じゅうやく</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>to soak, to pierce, to be deeply moved</t>
+          <t>executive</t>
         </is>
       </c>
     </row>
@@ -1821,17 +1833,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>資産</t>
+          <t>率直</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>しさん</t>
+          <t>そっちょく</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>asset</t>
+          <t>frank</t>
         </is>
       </c>
     </row>
@@ -1841,17 +1853,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>体つき</t>
+          <t>深刻化</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>からだつき</t>
+          <t>しんこくか</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>build</t>
+          <t>becoming more serious</t>
         </is>
       </c>
     </row>
@@ -1861,17 +1873,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>定期預金</t>
+          <t>恨む</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ていきよきん</t>
+          <t>うらむ</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>time deposit</t>
+          <t>to hold a grudge</t>
         </is>
       </c>
     </row>
@@ -1881,17 +1893,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>訴えかける</t>
+          <t>伝染</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>うったえかける</t>
+          <t>でんせん</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>to appeal</t>
+          <t>infection</t>
         </is>
       </c>
     </row>
@@ -1901,17 +1913,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>宣伝費</t>
+          <t>取引先</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>せんでんひ</t>
+          <t>とりひきさき</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>advertising cost</t>
+          <t>customer, business acquaintance</t>
         </is>
       </c>
     </row>
@@ -1921,17 +1933,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>仕事ぶり</t>
+          <t>就任</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>しごとぶり</t>
+          <t>しゅうにん</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>job performance, way of working</t>
+          <t>inauguration, taking up a post</t>
         </is>
       </c>
     </row>
@@ -1941,17 +1953,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>真向い</t>
+          <t>言い張る</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>まむかい</t>
+          <t>いいはる</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>right opposite</t>
+          <t>to insist on, to stick to one's point</t>
         </is>
       </c>
     </row>
@@ -1961,17 +1973,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>気を取られる</t>
+          <t>訂正</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>きをとられる</t>
+          <t>ていせい</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>to be distracted</t>
+          <t>correction</t>
         </is>
       </c>
     </row>
@@ -1981,17 +1993,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>手につかない</t>
+          <t>今にも</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>てにつかない</t>
+          <t>いまにも</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>can't focus [concentrate] on</t>
+          <t>at any moment</t>
         </is>
       </c>
     </row>
@@ -2001,17 +2013,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>日ごろ</t>
+          <t>気を取られる</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ひごろ</t>
+          <t>きをとられる</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>usually</t>
+          <t>to be distracted</t>
         </is>
       </c>
     </row>
@@ -2021,17 +2033,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>献立</t>
+          <t>何となく</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>こんだて</t>
+          <t>なんとなく</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>menu</t>
+          <t>for some reason or other</t>
         </is>
       </c>
     </row>
@@ -2041,17 +2053,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>意義深い</t>
+          <t>著名人</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>いぎぶかい</t>
+          <t>ちょめいじん</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>significant</t>
+          <t>celebrity</t>
         </is>
       </c>
     </row>
@@ -2061,17 +2073,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>伝言</t>
+          <t>一日おき</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>でんごん</t>
+          <t>いちにちおき</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>(verbal) message</t>
+          <t>every other day</t>
         </is>
       </c>
     </row>
@@ -2081,17 +2093,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>中でも</t>
+          <t>児童</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>なかでも</t>
+          <t>じどう</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>most especially</t>
+          <t>child</t>
         </is>
       </c>
     </row>
@@ -2101,17 +2113,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>頭に来る</t>
+          <t>幾分</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>あたまにくる</t>
+          <t>いくぶん</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>to get mad</t>
+          <t>somewhat</t>
         </is>
       </c>
     </row>
@@ -2121,17 +2133,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>気が向く</t>
+          <t>引き分け</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>きがむく</t>
+          <t>ひきわけ</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>to feel like</t>
+          <t>to draw</t>
         </is>
       </c>
     </row>
@@ -2141,17 +2153,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>及ぶ</t>
+          <t>負担</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>およぶ</t>
+          <t>ふたん</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>to reach, to extend</t>
+          <t>burden, responsibility</t>
         </is>
       </c>
     </row>
@@ -2161,17 +2173,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>差しかかる</t>
+          <t>納める</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>さしかかる</t>
+          <t>おさめる</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>to approach</t>
+          <t>to pay</t>
         </is>
       </c>
     </row>
@@ -2181,17 +2193,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>初公開</t>
+          <t>手が出ない</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>はつこうかい</t>
+          <t>てがでない</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>first public exhibition</t>
+          <t>to be out of one's reach</t>
         </is>
       </c>
     </row>
@@ -2201,17 +2213,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>申請</t>
+          <t>取り組み</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>しんせい</t>
+          <t>とりくみ</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>application</t>
+          <t>tackling</t>
         </is>
       </c>
     </row>
@@ -2221,17 +2233,17 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>刻む</t>
+          <t>体つき</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>きざむ</t>
+          <t>からだつき</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>to chop</t>
+          <t>build</t>
         </is>
       </c>
     </row>
@@ -2241,17 +2253,17 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>挿入</t>
+          <t>普及</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>そうにゅう</t>
+          <t>ふきゅう</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>insertion</t>
+          <t>diffusion</t>
         </is>
       </c>
     </row>
@@ -2261,17 +2273,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>受け持つ</t>
+          <t>反比例</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>うけもつ</t>
+          <t>はんぴれい</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>to be in charge of</t>
+          <t>inverse proportion</t>
         </is>
       </c>
     </row>
@@ -2281,17 +2293,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>普及率</t>
+          <t>直ちに</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ふきゅうりつ</t>
+          <t>ただちに</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>diffusion rate</t>
+          <t>right away</t>
         </is>
       </c>
     </row>
@@ -2301,17 +2313,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>行方</t>
+          <t>伝言</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ゆくえ</t>
+          <t>でんごん</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>whereabouts</t>
+          <t>(verbal) message</t>
         </is>
       </c>
     </row>
@@ -2321,17 +2333,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>強気</t>
+          <t>受け持つ</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>つよき</t>
+          <t>うけもつ</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>strong, aggressive</t>
+          <t>to be in charge of</t>
         </is>
       </c>
     </row>
@@ -2341,17 +2353,17 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>絶えず</t>
+          <t>初公開</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>たえず</t>
+          <t>はつこうかい</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>constantly</t>
+          <t>first public exhibition</t>
         </is>
       </c>
     </row>
@@ -2361,17 +2373,17 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>執筆</t>
+          <t>気が利く</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>しっぴつ</t>
+          <t>きがきく</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>writing</t>
+          <t>smart</t>
         </is>
       </c>
     </row>
@@ -2381,17 +2393,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>初優勝</t>
+          <t>低下</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>はつゆうしょう</t>
+          <t>ていか</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>first victory</t>
+          <t>decrease</t>
         </is>
       </c>
     </row>
@@ -2401,17 +2413,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>恨む</t>
+          <t>刻む</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>うらむ</t>
+          <t>きざむ</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>to hold a grudge</t>
+          <t>to chop</t>
         </is>
       </c>
     </row>
@@ -2421,17 +2433,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>不作法</t>
+          <t>張り切る</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>ぶさほう</t>
+          <t>はりきる</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>impolite, rude</t>
+          <t>to be enthusiastic</t>
         </is>
       </c>
     </row>
@@ -2439,21 +2451,9 @@
       <c r="A103" s="1" t="n">
         <v>101</v>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>伝染</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>でんせん</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>infection</t>
-        </is>
-      </c>
+      <c r="B103" t="inlineStr"/>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
@@ -2461,17 +2461,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>行事</t>
+          <t>岬</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ぎょうじ</t>
+          <t>みさき</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>event</t>
+          <t>cape</t>
         </is>
       </c>
     </row>
@@ -2481,17 +2481,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>幾分</t>
+          <t>研修</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>いくぶん</t>
+          <t>けんしゅう</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>somewhat</t>
+          <t>training</t>
         </is>
       </c>
     </row>
@@ -2501,17 +2501,17 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>引き分け</t>
+          <t>庶民</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>ひきわけ</t>
+          <t>しょみん</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>to draw</t>
+          <t>ordinary people</t>
         </is>
       </c>
     </row>
@@ -2521,17 +2521,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>次第に</t>
+          <t>憲法</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>しだいに</t>
+          <t>けんぽう</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>gradually</t>
+          <t>constitution</t>
         </is>
       </c>
     </row>
@@ -2541,17 +2541,17 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>託児所</t>
+          <t>近々</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>たくじしょ</t>
+          <t>ちかぢか</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>nursery</t>
+          <t>shortly</t>
         </is>
       </c>
     </row>
@@ -2561,17 +2561,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>通りかかる</t>
+          <t>申請</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>とおりかかる</t>
+          <t>しんせい</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>to happen to pass by</t>
+          <t>application</t>
         </is>
       </c>
     </row>
@@ -2581,17 +2581,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>一段と</t>
+          <t>挿入</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>いちだんと</t>
+          <t>そうにゅう</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>even more</t>
+          <t>insertion</t>
         </is>
       </c>
     </row>
@@ -2601,17 +2601,17 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>手が出ない</t>
+          <t>強いる</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>てがでない</t>
+          <t>しいる</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>to be out of one's reach</t>
+          <t>to force, to thrust</t>
         </is>
       </c>
     </row>
@@ -2621,17 +2621,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>負担</t>
+          <t>差し支えない</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>ふたん</t>
+          <t>さしつかえない</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>burden, responsibility</t>
+          <t>having no objection</t>
         </is>
       </c>
     </row>
@@ -2641,17 +2641,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>前後</t>
+          <t>目に浮かぶ</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>ぜんご</t>
+          <t>めにうかぶ</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>around</t>
+          <t>to imagine, to picture in one's mind</t>
         </is>
       </c>
     </row>
@@ -2661,17 +2661,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>補う</t>
+          <t>承諾</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>おぎなう</t>
+          <t>しょうだく</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>to make up for</t>
+          <t>acceptance</t>
         </is>
       </c>
     </row>
@@ -2681,17 +2681,17 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>副作用</t>
+          <t>打ち消す</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ふくさよう</t>
+          <t>うちけす</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>side effect</t>
+          <t>to deny, to contradict</t>
         </is>
       </c>
     </row>
@@ -2701,857 +2701,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>何となく</t>
+          <t>別荘</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>なんとなく</t>
+          <t>べっそう</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>for some reason or other</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="1" t="n">
-        <v>115</v>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>攻める</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>せめる</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>to attack</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="1" t="n">
-        <v>116</v>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>一日おき</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>いちにちおき</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>every other day</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="1" t="n">
-        <v>117</v>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>憲法</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>けんぽう</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>constitution</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="1" t="n">
-        <v>118</v>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>気に食わない</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>きにくわない</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>to dislike</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="1" t="n">
-        <v>119</v>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>率直</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>そっちょく</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>frank</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="1" t="n">
-        <v>120</v>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>打ち消す</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>うちけす</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>to deny, to contradict</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="1" t="n">
-        <v>121</v>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>気が利く</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>きがきく</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>smart</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="1" t="n">
-        <v>122</v>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>交際</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>こうさい</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>association</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="1" t="n">
-        <v>123</v>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>見出し</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>みだし</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>headline</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="1" t="n">
-        <v>124</v>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>不景気</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>ふけいき</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>recession</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="1" t="n">
-        <v>125</v>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>貯蓄</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>ちょちく</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>savings</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="1" t="n">
-        <v>126</v>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>差し押さえる</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>さしおさえる</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>to seize</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="1" t="n">
-        <v>127</v>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>取り組み</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>とりくみ</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>tackling</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="1" t="n">
-        <v>128</v>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>担ぐ</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>かつぐ</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>to carry on one's shoulder</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="1" t="n">
-        <v>129</v>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>低下</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>ていか</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>decrease</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="1" t="n">
-        <v>130</v>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>豊富</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>ほうふ</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>abundance</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="1" t="n">
-        <v>131</v>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>築く</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>きずく</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>to build</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="1" t="n">
-        <v>132</v>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>索引</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>さくいん</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>index</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="1" t="n">
-        <v>133</v>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>重役</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>じゅうやく</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>executive</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="1" t="n">
-        <v>134</v>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>汚染</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>おせん</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>pollution</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="1" t="n">
-        <v>135</v>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>通信網</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>つうしんもう</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>communication network</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="1" t="n">
-        <v>136</v>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>引用</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>いんよう</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>citation, quotation</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="1" t="n">
-        <v>137</v>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>手が掛かる</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>てがかかる</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>difficult</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="1" t="n">
-        <v>138</v>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>採点</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>さいてん</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>scoring</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="1" t="n">
-        <v>139</v>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>案の定</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>あんのじょう</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>as expected</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="1" t="n">
-        <v>140</v>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>引っかかる</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>ひっかかる</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>to be stuck, to get caught</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="1" t="n">
-        <v>141</v>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>著名人</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>ちょめいじん</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>celebrity</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="1" t="n">
-        <v>142</v>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>敗れる</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>やぶれる</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>to be beaten [defeated]</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="1" t="n">
-        <v>143</v>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>否定</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>ひてい</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>negation, denial</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="1" t="n">
-        <v>144</v>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>資本金</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>しほんきん</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="1" t="n">
-        <v>145</v>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>微量</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>びりょう</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>very small amount</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="1" t="n">
-        <v>146</v>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>庶民</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>しょみん</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>ordinary people</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="1" t="n">
-        <v>147</v>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>引き受ける</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>ひきうける</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>to undertake</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="1" t="n">
-        <v>148</v>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>性能</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>せいのう</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>performance</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="1" t="n">
-        <v>149</v>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>果たして</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>はたして</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>sure enough, as expected</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="1" t="n">
-        <v>150</v>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>目に浮かぶ</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>めにうかぶ</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>to imagine, to picture in one's mind</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="1" t="n">
-        <v>151</v>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>従来</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>じゅうらい</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>conventional</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="1" t="n">
-        <v>152</v>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>取引先</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>とりひきさき</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>customer, business acquaintance</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="1" t="n">
-        <v>153</v>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>利子</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>りし</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>interest</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="1" t="n">
-        <v>154</v>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>超大作</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>ちょうたいさく</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>blockbuster</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="1" t="n">
-        <v>155</v>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>納める</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>おさめる</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>to pay</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="1" t="n">
-        <v>156</v>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>保証金</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>ほしょうきん</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>deposit</t>
+          <t>cottage, villa</t>
         </is>
       </c>
     </row>
